--- a/03_Outputs/Minero_Agroecologica/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Minero_Agroecologica/02_Demografia/demografia.xlsx
@@ -2153,7 +2153,7 @@
         <v>10.8004378457241</v>
       </c>
       <c r="F8" s="83">
-        <v>5.53694957576995</v>
+        <v>5.53694957576996</v>
       </c>
       <c r="G8" s="85">
         <v>25.6793750880495</v>
